--- a/lotti/LOTTO_0005.xlsx
+++ b/lotti/LOTTO_0005.xlsx
@@ -70,6 +70,21 @@
     <t/>
   </si>
   <si>
+    <t>Kit Seconda Trasferta Juventus</t>
+  </si>
+  <si>
+    <t>20262027尤文主场球迷版</t>
+  </si>
+  <si>
+    <t>Kit</t>
+  </si>
+  <si>
+    <t>XXL: (NICOLOSI, 21)</t>
+  </si>
+  <si>
+    <t>Serie A</t>
+  </si>
+  <si>
     <t>Tuta Zip Intera Manchester United Nera e Rossa</t>
   </si>
   <si>
@@ -83,9 +98,6 @@
   </si>
   <si>
     <t>20262027米兰客场球迷版</t>
-  </si>
-  <si>
-    <t>Kit</t>
   </si>
   <si>
     <t>M: (PULISIC, 11)</t>
@@ -218,18 +230,6 @@
   </si>
   <si>
     <t>XL: (MN, 17)</t>
-  </si>
-  <si>
-    <t>Kit Seconda Trasferta Juventus</t>
-  </si>
-  <si>
-    <t>20262027尤文主场球迷版</t>
-  </si>
-  <si>
-    <t>XXL: (NICOLOSI, 21)</t>
-  </si>
-  <si>
-    <t>Serie a</t>
   </si>
   <si>
     <t>Total Quantity (pcs)</t>
@@ -366,14 +366,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1034599</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -395,8 +400,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="958399"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -404,15 +409,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1034599</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -434,8 +444,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="2075999"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -443,15 +453,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1034599</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -473,8 +488,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="3193599"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -482,15 +497,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1034599</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -512,8 +532,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="4311199"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -521,15 +541,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1034599</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -551,8 +576,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="5428799"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -560,15 +585,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>46000</xdr:rowOff>
+      <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Picture 6">
@@ -590,8 +620,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="6546400"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -599,15 +629,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>44000</xdr:rowOff>
+      <xdr:rowOff>46000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1036600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Picture 7">
@@ -629,8 +664,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="7666000"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -638,15 +673,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Picture 8">
@@ -668,8 +708,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="8832400"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -677,15 +717,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Picture 9">
@@ -707,8 +752,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="9950000"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -716,15 +761,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Picture 10">
@@ -746,8 +796,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="11067600"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -755,15 +805,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Picture 11">
@@ -785,8 +840,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="12185200"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -794,15 +849,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="12" name="Picture 12">
@@ -824,8 +884,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="13302800"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -833,15 +893,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>73000</xdr:rowOff>
+      <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="13" name="Picture 13">
@@ -863,8 +928,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="14420400"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -872,15 +937,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>44000</xdr:rowOff>
+      <xdr:rowOff>73000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1063600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="14" name="Picture 14">
@@ -902,8 +972,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="15567000"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -911,15 +981,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="15" name="Picture 15">
@@ -941,8 +1016,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="17392200"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -950,15 +1025,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="16" name="Picture 16">
@@ -980,8 +1060,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="18509800"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -989,15 +1069,20 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>16000</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>44000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="990600" cy="990600"/>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1006600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1034600</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="17" name="Picture 17">
@@ -1019,8 +1104,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="16000" y="19627400"/>
+          <a:ext cx="990600" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1028,7 +1113,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1513,8 +1598,8 @@
       <c r="E4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5">
-        <v>1</v>
+      <c r="F4" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>18</v>
@@ -1522,8 +1607,8 @@
       <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>18</v>
+      <c r="I4" s="5">
+        <v>1</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>18</v>
@@ -1562,16 +1647,16 @@
         <v>1</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X4" s="7">
-        <v>26</v>
+        <v>8.3</v>
       </c>
       <c r="Y4" s="7">
-        <v>26</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="5" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1579,13 +1664,13 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>18</v>
@@ -1639,16 +1724,16 @@
         <v>1</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="W5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="X5" s="7">
-        <v>6.86</v>
+        <v>26</v>
       </c>
       <c r="Y5" s="7">
-        <v>8.86</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1656,13 +1741,13 @@
         <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>18</v>
@@ -1716,16 +1801,16 @@
         <v>1</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="X6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1733,13 +1818,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>18</v>
@@ -1799,10 +1884,10 @@
         <v>18</v>
       </c>
       <c r="X7" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1810,230 +1895,230 @@
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="W8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="X8" s="7">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" s="5">
+        <v>1</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="W9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="7">
+        <v>14</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="92" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U8" s="5">
-        <v>1</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="W8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="X8" s="7">
-        <v>14</v>
-      </c>
-      <c r="Y8" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="92" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5">
         <v>3</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U9" s="5">
+      <c r="G10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U10" s="5">
         <v>4</v>
       </c>
-      <c r="V9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="X9" s="7">
+      <c r="V10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="X10" s="7">
         <v>8.99</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y10" s="7">
         <v>43.96</v>
-      </c>
-    </row>
-    <row r="10" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U10" s="5">
-        <v>1</v>
-      </c>
-      <c r="V10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="W10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="X10" s="7">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="7">
-        <v>10</v>
       </c>
     </row>
     <row r="11" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2041,19 +2126,19 @@
         <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>18</v>
@@ -2107,10 +2192,10 @@
         <v>18</v>
       </c>
       <c r="X11" s="7">
-        <v>9.99</v>
+        <v>8</v>
       </c>
       <c r="Y11" s="7">
-        <v>11.99</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2124,7 +2209,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
@@ -2178,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W12" s="6" t="s">
         <v>18</v>
@@ -2195,13 +2280,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>18</v>
@@ -2255,7 +2340,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W13" s="6" t="s">
         <v>18</v>
@@ -2272,22 +2357,22 @@
         <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1</v>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>18</v>
@@ -2332,16 +2417,16 @@
         <v>1</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="W14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="X14" s="7">
-        <v>22</v>
+        <v>9.99</v>
       </c>
       <c r="Y14" s="7">
-        <v>22</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2349,13 +2434,13 @@
         <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>18</v>
@@ -2415,27 +2500,27 @@
         <v>18</v>
       </c>
       <c r="X15" s="7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Y15" s="7">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="16" ht="146" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="5">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>18</v>
@@ -2443,11 +2528,11 @@
       <c r="G16" s="5">
         <v>1</v>
       </c>
-      <c r="H16" s="5">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5">
-        <v>1</v>
+      <c r="H16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>18</v>
@@ -2483,10 +2568,10 @@
         <v>18</v>
       </c>
       <c r="U16" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="W16" s="6" t="s">
         <v>18</v>
@@ -2495,84 +2580,84 @@
         <v>8</v>
       </c>
       <c r="Y16" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="146" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U17" s="5">
+        <v>7</v>
+      </c>
+      <c r="V17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="W17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="X17" s="7">
+        <v>8</v>
+      </c>
+      <c r="Y17" s="7">
         <v>70</v>
-      </c>
-    </row>
-    <row r="17" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U17" s="5">
-        <v>1</v>
-      </c>
-      <c r="V17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="W17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="X17" s="7">
-        <v>8.3</v>
-      </c>
-      <c r="Y17" s="7">
-        <v>10.3</v>
       </c>
     </row>
     <row r="18" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2580,25 +2665,25 @@
         <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>18</v>
+      <c r="F18" s="5">
+        <v>1</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="5">
-        <v>1</v>
+      <c r="H18" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>18</v>
@@ -2640,16 +2725,16 @@
         <v>1</v>
       </c>
       <c r="V18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="X18" s="7">
-        <v>9.99</v>
+        <v>8.3</v>
       </c>
       <c r="Y18" s="7">
-        <v>12.99</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="19" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2663,7 +2748,7 @@
         <v>64</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>18</v>
@@ -2720,13 +2805,13 @@
         <v>65</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="X19" s="7">
-        <v>8</v>
+        <v>9.99</v>
       </c>
       <c r="Y19" s="7">
-        <v>10</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="20" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -2734,13 +2819,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>18</v>
@@ -2751,11 +2836,11 @@
       <c r="G20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="5">
-        <v>1</v>
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>18</v>
@@ -2794,16 +2879,16 @@
         <v>1</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W20" s="6" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="X20" s="7">
-        <v>6.86</v>
+        <v>8</v>
       </c>
       <c r="Y20" s="7">
-        <v>9.86</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
@@ -2835,7 +2920,7 @@
       </c>
       <c r="Y21" s="10">
         <f>SUM(Y4:Y20)</f>
-        <v>296.94</v>
+        <v>299.52</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
@@ -2893,7 +2978,7 @@
       <c r="T23" s="8"/>
       <c r="Y23" s="12">
         <f>Y21+Y22</f>
-        <v>380.94</v>
+        <v>383.52</v>
       </c>
     </row>
   </sheetData>
